--- a/survey_templates/036_workplace_technology_survey--survey_templates.xlsx
+++ b/survey_templates/036_workplace_technology_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What is your current job title?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How many years of experience do you have in the field?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What is your current role in the company?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What is your department/section in the company?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How would you rate your satisfaction with our company's technology and tools?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you use the company email system?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How satisfied are you with the company's IT services?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you use the company's collaboration tools (e.g., Slack, Trello, Asana)?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you experience issues with the company's technology?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How many hours of work do you think you spend using digital tools each day?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you experience delays or obstacles in your work due to technology issues?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How satisfied are you with the company's workflow and process?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you use the company's time-tracking tools (e.g., Harvest, Clockify)?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How many hours do you think you could save with more efficient technology?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you receive unnecessary notifications from the company's technology?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What technology-related features would you like to see implemented or improved?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you use the company's mobile app?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How satisfied are you with the company's IT support team?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What technology-related challenges do you face in your work?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How many IT-related issues do you think the company should address to improve?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What is the most important technology-related feature or improvement you would like to see?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How often do you share your IT-related concerns with colleagues or management?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>How satisfied are you with the overall technology used in the company?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What technology-related feedback would you like to give to the company?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>workplace-technology-survey</t>
+          <t>What is your overall satisfaction with the company's technology?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +1126,901 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_3_choices</t>
+          <t>workplace_technology_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_3_choices</t>
+          <t>workplace_technology_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_4_choices</t>
+          <t>workplace_technology_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_4_choices</t>
+          <t>workplace_technology_survey_page_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_11_choices</t>
+          <t>workplace_technology_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_11_choices</t>
+          <t>workplace_technology_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_12_choices</t>
+          <t>workplace_technology_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_12_choices</t>
+          <t>workplace_technology_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_19_choices</t>
+          <t>workplace_technology_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_19_choices</t>
+          <t>workplace_technology_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_20_choices</t>
+          <t>workplace_technology_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>workplace_technology_survey_page_20_choices</t>
+          <t>workplace_technology_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Regularly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_8_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>almost_always</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Almost Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>regularly</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Regularly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>almost_always</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Almost Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Very satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Somewhat satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Somewhat dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Very dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_13_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_13_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_13_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>regularly</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Regularly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_13_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>almost_always</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Almost Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>regularly</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Regularly</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>almost_always</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Almost Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>regularly</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Regularly</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>almost_always</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Almost Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Very satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Somewhat satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Somewhat dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_18_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Very dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_22_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_22_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_22_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_22_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>regularly</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Regularly</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_22_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>almost_always</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Almost Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_25_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Very satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_25_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Somewhat satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_25_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_25_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Somewhat dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>workplace_technology_survey_page_25_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
